--- a/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_67601_completo.xlsx
+++ b/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_67601_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1b7e153ab46346cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4d6391747b534e7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,7 +255,172 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">

--- a/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_67601_completo.xlsx
+++ b/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_67601_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4d6391747b534e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2987a0cee4d8446e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1074,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.5028</x:v>
+        <x:v>      3.2880</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,28 +1794,403 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      3.2880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4783</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3867</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      5.8571</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.6198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
+          <x:t>02/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1120,381 +2200,6 @@
       </x:c>
       <x:c s="3">
         <x:v>      5.8571</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.5933</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.5933</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.3438</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.4958</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.4958</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.9328</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.4958</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.6034</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.7122</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.7122</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.1577</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.6198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.0984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.0984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.8220</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.2717</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.2717</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.1577</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.3867</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.3867</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.3867</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.6198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.8571</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.0984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.0984</x:v>
       </x:c>
     </x:row>
     <x:row>
